--- a/business_forms/047_project_status_report_form--business_forms.xlsx
+++ b/business_forms/047_project_status_report_form--business_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -437,12 +437,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E19"/>
+  <dimension ref="A1:E15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="17" customWidth="1" min="1" max="1"/>
-    <col width="17" customWidth="1" min="2" max="2"/>
-    <col width="17" customWidth="1" min="3" max="3"/>
+    <col width="12" customWidth="1" min="1" max="1"/>
+    <col width="21" customWidth="1" min="2" max="2"/>
+    <col width="21" customWidth="1" min="3" max="3"/>
     <col width="6" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
   </cols>
@@ -525,7 +525,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>project_status</t>
+          <t>Project Status</t>
         </is>
       </c>
       <c r="D4" t="inlineStr"/>
@@ -548,13 +548,13 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>start_date</t>
+          <t>Start Date</t>
         </is>
       </c>
       <c r="D5" t="inlineStr"/>
       <c r="E5" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -571,13 +571,13 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>end_date</t>
+          <t>End Date</t>
         </is>
       </c>
       <c r="D6" t="inlineStr"/>
       <c r="E6" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -594,36 +594,36 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>project_manager</t>
+          <t>Project Manager</t>
         </is>
       </c>
       <c r="D7" t="inlineStr"/>
       <c r="E7" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>select_multiple</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>project_status</t>
+          <t>project_progress</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>project_status</t>
+          <t>Project Progress</t>
         </is>
       </c>
       <c r="D8" t="inlineStr"/>
       <c r="E8" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -635,18 +635,18 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>progress</t>
+          <t>project_challenges</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>progress</t>
+          <t>Project Challenges</t>
         </is>
       </c>
       <c r="D9" t="inlineStr"/>
       <c r="E9" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -658,35 +658,35 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>challenges</t>
+          <t>project_comments</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>challenges</t>
+          <t>Project Comments</t>
         </is>
       </c>
       <c r="D10" t="inlineStr"/>
       <c r="E10" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>comments</t>
+          <t>assigned_tool</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>comments</t>
+          <t>Assigned Tool</t>
         </is>
       </c>
       <c r="D11" t="inlineStr"/>
@@ -699,23 +699,23 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>select_one</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>assigned_tool</t>
+          <t>project_category</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>assigned_tool</t>
+          <t>Project Category</t>
         </is>
       </c>
       <c r="D12" t="inlineStr"/>
       <c r="E12" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -727,18 +727,18 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>category</t>
+          <t>project_description</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>category</t>
+          <t>Project Description</t>
         </is>
       </c>
       <c r="D13" t="inlineStr"/>
       <c r="E13" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -750,18 +750,18 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>description</t>
+          <t>output_file</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>description</t>
+          <t>Output File</t>
         </is>
       </c>
       <c r="D14" t="inlineStr"/>
       <c r="E14" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -773,110 +773,18 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>output_file</t>
+          <t>form_id</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>output_file</t>
+          <t>Form ID</t>
         </is>
       </c>
       <c r="D15" t="inlineStr"/>
       <c r="E15" t="inlineStr">
         <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>form_ids</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>form_ids</t>
-        </is>
-      </c>
-      <c r="D16" t="inlineStr"/>
-      <c r="E16" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>description</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>description</t>
-        </is>
-      </c>
-      <c r="D17" t="inlineStr"/>
-      <c r="E17" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>form_ids</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>form_ids</t>
-        </is>
-      </c>
-      <c r="D18" t="inlineStr"/>
-      <c r="E18" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>output_file</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>output_file</t>
-        </is>
-      </c>
-      <c r="D19" t="inlineStr"/>
-      <c r="E19" t="inlineStr">
-        <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -891,12 +799,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C10"/>
+  <dimension ref="A1:C8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
-    <col width="9" customWidth="1" min="2" max="2"/>
-    <col width="9" customWidth="1" min="3" max="3"/>
+    <col width="11" customWidth="1" min="2" max="2"/>
+    <col width="11" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -924,12 +832,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>option1</t>
+          <t>on_going</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>option1</t>
+          <t>On Going</t>
         </is>
       </c>
     </row>
@@ -941,12 +849,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>option2</t>
+          <t>completed</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>option2</t>
+          <t>Completed</t>
         </is>
       </c>
     </row>
@@ -958,12 +866,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>option3</t>
+          <t>cancelled</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>option3</t>
+          <t>Cancelled</t>
         </is>
       </c>
     </row>
@@ -975,46 +883,46 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>option1</t>
+          <t>delayed</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>option1</t>
+          <t>Delayed</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>project_status_choices</t>
+          <t>assigned_tool_choices</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>option2</t>
+          <t>tool_1</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>option2</t>
+          <t>Tool 1</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>project_status_choices</t>
+          <t>assigned_tool_choices</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>option3</t>
+          <t>tool_2</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>option3</t>
+          <t>Tool 2</t>
         </is>
       </c>
     </row>
@@ -1026,46 +934,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>option1</t>
+          <t>tool_3</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>option1</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>assigned_tool_choices</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>option2</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>option2</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>assigned_tool_choices</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>option3</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>option3</t>
+          <t>Tool 3</t>
         </is>
       </c>
     </row>
